--- a/examples/ml_results/ml_results_example.xlsx
+++ b/examples/ml_results/ml_results_example.xlsx
@@ -10,7 +10,141 @@
 </x:workbook>
 </file>
 
-<file path=xl/sharedStrings.xml>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="44">
+  <x:si>
+    <x:t>Deep Learning Model Performance Comparison</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Neural Network Architecture Benchmark</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Model Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Parameters (M)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Training Time (hrs)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Inference Speed (imgs/sec)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ImageNet Top-1 Acc %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ImageNet Top-5 Acc %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COCO mAP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Memory (GB)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResNet-50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ResNet-101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EfficientNet-B0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EfficientNet-B4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vision Transformer-B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YOLO-v8n</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YOLO-v8s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YOLO-v8m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Swin-Transformer-T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ConvNeXt-T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Model Performance Analysis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Params (M)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Accuracy (Top-1 %)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Efficiency Score</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Params-per-Accuracy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Speed Ranking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Accuracy Gain vs ResNet-50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Memory per Accuracy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Training Progress - Loss and Accuracy</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epoch</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Training Loss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Validation Loss</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Training Accuracy %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Validation Accuracy %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Learning Rate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Overfitting Gap (Val-Train)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hyperparameter Tuning Results</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Experiment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Batch Size</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weight Decay</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warmup Steps</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Final Accuracy %</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Convergence Time (hrs)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Accuracy per Hour</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,7 +203,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:t>Training vs Validation Accuracy Over Epochs</a:t>
+              <a:t>Model Parameters vs Accuracy Trade-off</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -77,12 +211,12 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:scatterChart>
+        <c:scatterStyle val="marker"/>
         <c:varyColors val="0"/>
         <c:axId val="100000000"/>
         <c:axId val="100000001"/>
-      </c:lineChart>
+      </c:scatterChart>
       <c:catAx>
         <c:axId val="100000000"/>
         <c:scaling>
@@ -114,7 +248,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
-              <a:t>Model Parameters vs Accuracy Trade-off</a:t>
+              <a:t>Training vs Validation Accuracy Over Epochs</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -122,12 +256,12 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:scatterChart>
-        <c:scatterStyle val="marker"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:axId val="100000000"/>
         <c:axId val="100000001"/>
-      </c:scatterChart>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="100000000"/>
         <c:scaling>

--- a/examples/ml_results/ml_results_example.xlsx
+++ b/examples/ml_results/ml_results_example.xlsx
@@ -300,7 +300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData>
+  <sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
         <x:v>0</x:v>
@@ -597,13 +597,13 @@
         <x:v>3.3</x:v>
       </x:c>
     </x:row>
-  </x:sheetData>
+  </sheetData>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData>
+  <sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
         <x:v>20</x:v>
@@ -865,13 +865,13 @@
         <x:f>=B13*1.5/(C13-50)</x:f>
       </x:c>
     </x:row>
-  </x:sheetData>
+  </sheetData>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData>
+  <sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
         <x:v>28</x:v>
@@ -1107,13 +1107,13 @@
         <x:f>=C12-B12</x:f>
       </x:c>
     </x:row>
-  </x:sheetData>
+  </sheetData>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData>
+  <sheetData>
     <x:row r="1">
       <x:c r="A1" t="s">
         <x:v>36</x:v>
@@ -1353,6 +1353,6 @@
         <x:f>=F11/G11</x:f>
       </x:c>
     </x:row>
-  </x:sheetData>
+  </sheetData>
 </x:worksheet>
 </file>